--- a/research/traditional_assets/database/data/hungary/hungary_beverage_soft.xlsx
+++ b/research/traditional_assets/database/data/hungary/hungary_beverage_soft.xlsx
@@ -587,26 +587,23 @@
           <t>Beverage (Soft)</t>
         </is>
       </c>
-      <c r="D2">
-        <v>-0.588</v>
-      </c>
       <c r="G2">
-        <v>-40.125</v>
+        <v>-18.09523809523809</v>
       </c>
       <c r="H2">
-        <v>-40.125</v>
+        <v>-18.09523809523809</v>
       </c>
       <c r="I2">
-        <v>-37.5</v>
+        <v>-19.52380952380952</v>
       </c>
       <c r="J2">
-        <v>-37.5</v>
+        <v>-19.52380952380952</v>
       </c>
       <c r="K2">
-        <v>-0.239</v>
+        <v>-0.41</v>
       </c>
       <c r="L2">
-        <v>-29.875</v>
+        <v>-19.52380952380952</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +627,70 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="V2">
-        <v>0.0009966777408637875</v>
+        <v>0.0006369426751592356</v>
       </c>
       <c r="W2">
-        <v>-0.3854838709677419</v>
+        <v>-0.9360730593607305</v>
       </c>
       <c r="X2">
-        <v>0.06315911353205982</v>
+        <v>0.112059570476388</v>
       </c>
       <c r="Y2">
-        <v>-0.4486429844998018</v>
+        <v>-1.048132629837119</v>
       </c>
       <c r="Z2">
-        <v>0.01333333333333333</v>
+        <v>0.04783599088838269</v>
       </c>
       <c r="AA2">
-        <v>-0.5</v>
+        <v>-0.9339407744874715</v>
       </c>
       <c r="AB2">
-        <v>0.06312862516658146</v>
+        <v>0.112059570476388</v>
       </c>
       <c r="AC2">
-        <v>-0.5631286251665815</v>
+        <v>-1.04600034496386</v>
       </c>
       <c r="AD2">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AG2">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AH2">
-        <v>0.0013271400132714</v>
+        <v>0</v>
       </c>
       <c r="AI2">
-        <v>0.009049773755656109</v>
+        <v>0</v>
       </c>
       <c r="AJ2">
-        <v>0.0003321155762205248</v>
+        <v>-0.0006373486297004461</v>
       </c>
       <c r="AK2">
-        <v>0.002277904328018223</v>
+        <v>-0.01176470588235294</v>
       </c>
       <c r="AL2">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AN2">
-        <v>-0.01652892561983471</v>
-      </c>
-      <c r="AO2">
-        <v>-300</v>
+        <v>-0</v>
       </c>
       <c r="AP2">
-        <v>-0.004132231404958678</v>
+        <v>0.002688172043010753</v>
       </c>
       <c r="AQ2">
-        <v>150</v>
+        <v>409.9999999999999</v>
       </c>
     </row>
     <row r="3">
@@ -715,26 +709,23 @@
           <t>Beverage (Soft)</t>
         </is>
       </c>
-      <c r="D3">
-        <v>-0.588</v>
-      </c>
       <c r="G3">
-        <v>-40.125</v>
+        <v>-18.09523809523809</v>
       </c>
       <c r="H3">
-        <v>-40.125</v>
+        <v>-18.09523809523809</v>
       </c>
       <c r="I3">
-        <v>-37.5</v>
+        <v>-19.52380952380952</v>
       </c>
       <c r="J3">
-        <v>-37.5</v>
+        <v>-19.52380952380952</v>
       </c>
       <c r="K3">
-        <v>-0.239</v>
+        <v>-0.41</v>
       </c>
       <c r="L3">
-        <v>-29.875</v>
+        <v>-19.52380952380952</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +749,70 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.003</v>
+        <v>0.001</v>
       </c>
       <c r="V3">
-        <v>0.0009966777408637875</v>
+        <v>0.0006369426751592356</v>
       </c>
       <c r="W3">
-        <v>-0.3854838709677419</v>
+        <v>-0.9360730593607305</v>
       </c>
       <c r="X3">
-        <v>0.06315911353205982</v>
+        <v>0.112059570476388</v>
       </c>
       <c r="Y3">
-        <v>-0.4486429844998018</v>
+        <v>-1.048132629837119</v>
       </c>
       <c r="Z3">
-        <v>0.01333333333333333</v>
+        <v>0.04783599088838269</v>
       </c>
       <c r="AA3">
-        <v>-0.5</v>
+        <v>-0.9339407744874715</v>
       </c>
       <c r="AB3">
-        <v>0.06312862516658146</v>
+        <v>0.112059570476388</v>
       </c>
       <c r="AC3">
-        <v>-0.5631286251665815</v>
+        <v>-1.04600034496386</v>
       </c>
       <c r="AD3">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0.004</v>
+        <v>0</v>
       </c>
       <c r="AG3">
-        <v>0.001</v>
+        <v>-0.001</v>
       </c>
       <c r="AH3">
-        <v>0.0013271400132714</v>
+        <v>0</v>
       </c>
       <c r="AI3">
-        <v>0.009049773755656109</v>
+        <v>0</v>
       </c>
       <c r="AJ3">
-        <v>0.0003321155762205248</v>
+        <v>-0.0006373486297004461</v>
       </c>
       <c r="AK3">
-        <v>0.002277904328018223</v>
+        <v>-0.01176470588235294</v>
       </c>
       <c r="AL3">
-        <v>0.001</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>-0.002</v>
+        <v>-0.001</v>
       </c>
       <c r="AN3">
-        <v>-0.01652892561983471</v>
-      </c>
-      <c r="AO3">
-        <v>-300</v>
+        <v>-0</v>
       </c>
       <c r="AP3">
-        <v>-0.004132231404958678</v>
+        <v>0.002688172043010753</v>
       </c>
       <c r="AQ3">
-        <v>150</v>
+        <v>409.9999999999999</v>
       </c>
     </row>
   </sheetData>
